--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dutch Bros Coffee</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Cloud Storage, Hive, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a91bd027b544af</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
+          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>AI/ML Data Scientist (GPSSC)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=178a3edf86886b28</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -876,12 +876,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed1a2a8d040517b</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS/Databricks - Mid Level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2f2bf8d80ebd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Cloud DevOps Programmer Analyst (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Seal Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=6418cc76af48cb9a</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,69 +1816,69 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, HBase, Scala, Kafka, Snowflake, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1610940d9ea365df</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, HBase, Scala, Kafka, Snowflake, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1610940d9ea365df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Fullstack</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, SQL Server, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb90dbd5192ef62</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Sr. Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Insygnum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c5dcc9f8e89ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=2c5dcc9f8e89ecd2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71acb476a93daa68</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
@@ -2708,25 +2708,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Backend Developer (Java) - Springfield</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>API Gateway, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681247860af931cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>Tobor Robot Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Django/Python</t>
+          <t>AI and vision learning engineer (In person required)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>SEC Industrial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e959c5c2ece017ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Backend Developer (Java) - Springfield</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+          <t>API Gateway, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=681247860af931cb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Database Systems Engineer</t>
+          <t>Enterprise Systems Engineer V</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Estuate</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,15 +3006,85 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Rogue Credit Union</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Medford, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Estuate</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Data Scientist (GPSSC)</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a3edf86886b28</t>
+          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Silverchair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
+          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silverchair</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
+          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Technical Architect (Java Microservices + React JS) - Springfield</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9a047238ed1e96c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect (Java Microservices + React JS) - Springfield</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a047238ed1e96c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ca5a09e7cef446</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud DevOps Programmer Analyst (Mid-Level or Senior)</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6418cc76af48cb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Cloud DevOps Programmer Analyst (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Seal Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=6418cc76af48cb9a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, HBase, Scala, Kafka, Snowflake, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1610940d9ea365df</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, HBase, Scala, Kafka, Snowflake, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1610940d9ea365df</t>
         </is>
       </c>
     </row>
@@ -2393,25 +2393,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - Platform &amp; Integrations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c5dcc9f8e89ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Senior Data Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=2c5dcc9f8e89ecd2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Sr Data Governance, Data Quality Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=cd5778480f15c573</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>AI and vision learning engineer (In person required)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>SEC Industrial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Developer (Java) - Springfield</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>API Gateway, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681247860af931cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Database Systems Engineer</t>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Estuate</t>
+          <t>Tobor Robot Corporation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,155 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Backend Developer (Java) - Springfield</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Photon</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Springfield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>API Gateway, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=681247860af931cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Enterprise Systems Engineer V</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rogue Credit Union</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Medford, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Estuate</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Silverchair</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
+          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect (Java Microservices + React JS) - Springfield</t>
+          <t>Data Architect III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a047238ed1e96c1</t>
+          <t>https://www.indeed.com/viewjob?jk=579dc28c4258841b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Silverchair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,242 +881,242 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Senior Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,269 +1161,269 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud DevOps Programmer Analyst (Mid-Level or Senior)</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6418cc76af48cb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer - Capital Markets Reference Data</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e85b21f1fb3187</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,94 +2211,94 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, HBase, Scala, Kafka, Snowflake, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1610940d9ea365df</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform &amp; Integrations</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cca2fb47a24092c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Consultant - Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Insygnum</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Glue, RDS, Hadoop, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add721e79e9d7463</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Developer</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c5dcc9f8e89ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Governance, Data Quality Analyst</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd5778480f15c573</t>
+          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,77 +2866,77 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,137 +3016,137 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=fe894b30da63db58</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20a5b3dd87476e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Developer (Java) - Springfield</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>API Gateway, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681247860af931cb</t>
+          <t>https://www.indeed.com/viewjob?jk=25a489bf0b432c45</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,40 +3191,565 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>Senior Analytics Engineer, Applied AI</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MDVIP LLC</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KPRMT Global solutions </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Delaware, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DEVELOPER L3(CONTRACT)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Product Data Analyst - Supply Chain</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AI and vision learning engineer (In person required)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SEC Industrial</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Peachtree Corners, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PNM</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data &amp; Integrations Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Alternate Solutions Health Network</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Parallel Domain</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Pacific, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Lake Data Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>E Source</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tobor Robot Corporation</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=841874e515da5e28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Enterprise Systems Engineer V</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Rogue Credit Union</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Medford, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>Database Systems Engineer</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Estuate</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Milpitas, CA, US USA</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D95" t="n">
         <v>10.4</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562c3953d5d4cf9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,49 +2771,49 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,24 +3006,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=fe894b30da63db58</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe894b30da63db58</t>
+          <t>https://www.indeed.com/viewjob?jk=3e20a5b3dd87476e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20a5b3dd87476e</t>
+          <t>https://www.indeed.com/viewjob?jk=25a489bf0b432c45</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25a489bf0b432c45</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>Tobor Robot Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>AI and vision learning engineer (In person required)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>SEC Industrial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
+          <t>Enterprise Systems Engineer V</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Rogue Credit Union</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Medford, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Database Systems Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Estuate</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3715,41 +3715,6 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Estuate</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CFRA Research</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b81c8f1c416031</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT Applications Engineer V - Data Science, Data &amp; AI Engineering, Application Engineering</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, ELT, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6453e30c37711925</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior DevOps Engineer - Atlanta, GA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca697f45b6290281</t>
+          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14b5f2f1affd1a2</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,104 +2201,104 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f774c4618ca5806</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777c988322e931b7</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Machine Learning Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,29 +2621,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,49 +2736,49 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Data Domain Architect Senior Associate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=25a489bf0b432c45</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e20a5b3dd87476e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25a489bf0b432c45</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
@@ -3303,25 +3303,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>TM1 Developer IBM Planning Analytics Solution</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t xml:space="preserve">KPRMT Global solutions </t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Delaware, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI and vision learning engineer (In person required)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>SEC Industrial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=841874e515da5e28</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Tobor Robot Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Advanced Analytics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, MySQL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8340f2d811ad9a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Database Systems Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Estuate</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,260 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Enterprise Systems Engineer V</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rogue Credit Union</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Medford, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Estuate</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,87 +573,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Engineer- Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>West Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Database DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Associate Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>ERC Pathlight</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8a7529cf2c2258</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect III</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=579dc28c4258841b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Silverchair</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Kafka, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03088aab7fd212d8</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Associate - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadb0e669ca658a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Reliability Engineer/Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CFRA Research</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b81c8f1c416031</t>
+          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>CFRA Research</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Database Administrator - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Atlanta, GA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a9d9f16c1afffa</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Sr Software Engineer (SQL/Databricks)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>CIBC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,104 +2201,104 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect IV (ATL)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Senior Associate</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,182 +2726,182 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Domain Architect Senior Associate</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Impala, Spark, Scala, Snowflake, Git, Python</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25a489bf0b432c45</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe894b30da63db58</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TM1 Developer IBM Planning Analytics Solution</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPRMT Global solutions </t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Delaware, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba25f8dea0287eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI and vision learning engineer (In person required)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SEC Industrial</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, NoSQL, ETL, Talend, Docker, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a87cdb9d826d513d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef09c50335c1ef7e</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, MLOps, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Advanced Analytics</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, MySQL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8340f2d811ad9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Data Lake Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>E Source</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tobor Robot Corporation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Product Data Analyst - Supply Chain Planning Platforms</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Spark, PySpark, Oracle, Power BI, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=39be9632789c9494</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Database Systems Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Estuate</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,192 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, Oracle, SQL Server, MySQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d7f5f64249cd00</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Enterprise Systems Engineer V</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Rogue Credit Union</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Medford, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technical QA Analyst II</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b752f77bb2fc7c7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Engineer</t>
+          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>Diality Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4c907044e720da</t>
+          <t>https://www.indeed.com/viewjob?jk=089debbb9a2ef97f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diality Inc</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089debbb9a2ef97f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Senior Engineer- Technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer- Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ERC Pathlight</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Medallion Architecture</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8a7529cf2c2258</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Stitch Consulting Services, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Sr Developer - Backend (Java Sprinboot) - Plano, TX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=147f2ed637995232</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer/Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, ECS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed2b2b5d3a2123b</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>CFRA Research</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d635caaec7baf168</t>
+          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CFRA Research</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Network Engineer/ PACS Admin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Radiology One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=780bff482e354d4c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Mid-Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, ETL, MLOps</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b371541d1ac53b</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Database Administrator - Mountlake Terrace, WA</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f72c836b506ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e79ac2cb00b1176b</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (SQL/Databricks)</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CIBC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59821689b0632a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,42 +2236,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>System Architect IV (ATL)</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0679e72962f96d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Dealpath</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7397c28f47e35c7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252844720ed3e114</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Software Engineer (Finance Team)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=030e43d608ff060a</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure (Robotics &amp; Cloud)</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tobor Robot Corporation</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Blob Storage, PostgreSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b311657af0452f37</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Enterprise Systems Engineer V</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Rogue Credit Union</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Medford, OR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technical QA Analyst II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,15 +4126,85 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technical QA Analyst II</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7b752f77bb2fc7c7</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud &amp; Digital Platform DevSecOps Engineer</t>
+          <t>Senior Engineer- Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diality Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089debbb9a2ef97f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE OPPORTUNITY)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebdb111545a743c</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer- Technology</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,77 +566,77 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>West Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Hartford, CT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
@@ -678,60 +678,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Database DevOps Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Zookeeper, Scala, Oracle, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9d74906a09ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stitch Consulting Services, Inc.</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e709ce8d08339ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdf4aa591683148</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Developer - Backend (Java Sprinboot) - Plano, TX</t>
+          <t>NLM Cloud Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147f2ed637995232</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CFRA Research</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CFRA Research</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Network Engineer/ PACS Admin</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Radiology One</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=780bff482e354d4c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Network Engineer/ PACS Admin</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Radiology One</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780bff482e354d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>NLM Cloud Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Lexical Intelligence, LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer, Global</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd7e80ca3c98167</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,29 +2376,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect IV - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dealpath</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645d3d76b515ea5a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7397c28f47e35c7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Software Engineering-Associate-Dallas</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce31ad37d0b4074e</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7397c28f47e35c7</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>Software Engineer, Finance Applications</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Software Engineer (Finance Team)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (Finance Team)</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Software Engineer III- ML</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c7049082ec88ec5c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=8831ab8789584700</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=030e43d608ff060a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RYZE Claim Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Senior Product Data Analyst - Supply Chain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Lake Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>E Source</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252a0ed8c082beed</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer II</t>
+          <t>Enterprise Systems Engineer V</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rogue Credit Union</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Medford, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Spark, PySpark, Scala, Snowflake, Data Modeling, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c35a1b6ab36700</t>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computing Architect (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=38348253fb6b3f9a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Hartford, CT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>West Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=13b7bf33022090df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Cloud Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hadoop, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7f43fcc961cf9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CFRA Research</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>CFRA Research</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Network Engineer/ PACS Admin</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Radiology One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780bff482e354d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Network Engineer/ PACS Admin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Radiology One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=780bff482e354d4c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer II</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hadoop, Spark, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49524b4a45bcb416</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=b66b03845fe2c951</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=b77e98c1795bddf7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer, Observe by Snowflake</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b918e60460b92ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,164 +2211,164 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Senior Development Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e881c656d4332d30</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Spark, Scala</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c607892a88eb133</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>System Architect IV - Onsite/Hybrid</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7397c28f47e35c7</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, Finance Applications</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, Oracle, MySQL, DynamoDB, Kubernetes, Git</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fb53ad2487f</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7397c28f47e35c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (Finance Team)</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,59 +2761,59 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,15 +2823,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Software Engineer III- ML</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Software Engineer (Finance Team)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545e32663300e2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,24 +3041,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c8d1f679e08f02</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7049082ec88ec5c</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8831ab8789584700</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8831ab8789584700</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RYZE Claim Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, Power BI, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d6a299e37b16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386fc1ac3272e529</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
@@ -3548,25 +3548,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Sr Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b5e31188e0caf7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Product Data Analyst - Supply Chain Planning Platforms</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Spark, PySpark, Oracle, Power BI, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39be9632789c9494</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Product Data Analyst - Supply Chain Planning Platforms</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Spark, PySpark, Oracle, Power BI, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=39be9632789c9494</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Business Intelligence Specialist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, Star Schema, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a5d9960a5b5f1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Snowflake, SQL Server, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0cc7c1bb617e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Technical QA Analyst II</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,15 +4196,190 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Enterprise Systems Engineer V</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Nightingale College</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Technical QA Analyst II</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7b752f77bb2fc7c7</t>
         </is>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Engineer- Technology</t>
+          <t>Azure Data Engineer with Power BI and C# .NET exp--Need Government domain</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Infopeople Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Queens, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a07efb549ef55e02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Computing Architect (Mid-Level or Senior)</t>
+          <t>Senior Engineer- Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38348253fb6b3f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae25761539c2b2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CFRA Research</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c6e589e7409759</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Network Engineer/ PACS Admin</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Radiology One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780bff482e354d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,94 +1851,94 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66b03845fe2c951</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77e98c1795bddf7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,59 +1966,59 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, dbt, Tableau, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceac9c56e064ddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Development Engineer (Core Engine)</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18eeecb282323a96</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7397c28f47e35c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Finance Team)</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8831ab8789584700</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,54 +3471,54 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Sr Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b5e31188e0caf7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Product Data Analyst - Supply Chain</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3527,46 +3527,46 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, PySpark, Scala, Oracle, Power BI</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3aaa95e1c534da</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b5e31188e0caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Product Data Analyst - Supply Chain Planning Platforms</t>
+          <t>Enterprise Systems Engineer V</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Spark, PySpark, Oracle, Power BI, CI/CD, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39be9632789c9494</t>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Specialist</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, Star Schema, Power BI, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a5d9960a5b5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Specialist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, Star Schema, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a5d9960a5b5f1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,217 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Enterprise Systems Engineer V</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Avalara</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Nightingale College</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Technical QA Analyst II</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b752f77bb2fc7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-29.xlsx
+++ b/results/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ingevity</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ingevity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=16901eb9125326fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Senior Software Engineer - Backend (Java)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ML Ops Engineer (AI)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SewerAI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brain Corp</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data</t>
+          <t>ML Ops Engineer (AI)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
+          <t>https://www.indeed.com/viewjob?jk=e33a68fd8e407bf9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Software Engineer II, Data Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brain Corp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Snowflake, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ae90714e471bca2a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Engineer, Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Medallion Architecture, GCP, Dataflow, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0932849bb0db18</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,15 +1913,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
+          <t>https://www.indeed.com/viewjob?jk=56f3e1e9f656a621</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9ab4d1357b520c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Python Full Stack Developer with Agentic AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>System Edge LLC.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Big Data Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M.P. Excavation LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMD Public-Dallas-Associate-Software Engineering</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Summer Intern Software Engineering, CloudOps</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>AMD Public-Dallas-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2afaac9488468d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Summer Intern Software Engineering, CloudOps</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=431a675e070ed1ad</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Product</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Software Engineer - Product</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec16e417da98d2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,15 +2858,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,49 +2911,49 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=7eb2c6707692ecc9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Business Intelligence Engineer</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b5e31188e0caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=329c033ba97dbb91</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Parallel Domain</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pacific, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>IT Data Platform Data Engineer (2 Openings)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PNM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Parallel Domain</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Pacific, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb764d6d9f3687d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Enterprise Systems Engineer V</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Specialist</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, Star Schema, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a5d9960a5b5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>Enterprise Systems Engineer V</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Avalara</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,17 +4161,157 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=738154f40eb68125</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Architect AI ML</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>3Pillar Global</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Nightingale College</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VTekis Consulting LLP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
         </is>
       </c>
     </row>
